--- a/astro-site/public/dl/haccp-templates/13-employee-hygiene-health-checklist.xlsx
+++ b/astro-site/public/dl/haccp-templates/13-employee-hygiene-health-checklist.xlsx
@@ -626,7 +626,7 @@
     <row r="12">
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>No federal food handler card exists. The FDA Food Code 2022 (§2-102.12) requires the person in charge to be a Certified Food Protection Manager (CFPM), and many states and counties also require a food handler card for staff: check what yours requires. What every inspection looks for is that the BUSINESS can show that its food handlers are trained and supervised. UK: there is no legal certificate; a Level 2 food hygiene course is the usual standard. Record this training in BONUS-01 (Food Safety Training Log).</t>
+          <t>No federal food handler card exists. Under the FDA Food Code 2022, at least one supervisory employee must be a Certified Food Protection Manager (CFPM, §2-102.12(A)), and many states and counties also require a food handler card for staff: check what yours requires. What every inspection looks for is that the BUSINESS can show that its food handlers are trained and supervised. UK: there is no legal certificate; a Level 2 food hygiene course is the usual standard. Record this training in BONUS-01 (Food Safety Training Log).</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
     <row r="16">
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>▸ Anyone with vomiting, diarrhea, fever, infected skin lesions or discharge must not handle food. They return to work 24 hours after the symptoms stop (FDA Food Code §2-201.13; UK: 48 hours, FSA).</t>
+          <t>▸ Report vomiting, diarrhea, jaundice, sore throat with fever, or an uncovered infected/draining wound. Vomiting or diarrhea: off food handling until 24 h symptom-free (§2-201.12, §2-201.13; UK: 48 h after symptoms stop). Sore throat with fever: back with a doctor's written clearance. Jaundice or a Big 6 diagnosis: excluded until the health department approves the return.</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
     <row r="25" ht="32" customHeight="1">
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>Tell the manager about vomiting, diarrhea, fever or a skin infection</t>
+          <t>Tell the manager about vomiting, diarrhea, jaundice, sore throat with fever or an infected/draining wound</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -934,7 +934,7 @@
     <row r="26" ht="32" customHeight="1">
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>Do not work with gastrointestinal symptoms until 24 hours after they stop (UK: 48 hours)</t>
+          <t>Vomiting or diarrhea: no food handling until 24 h symptom-free (UK: 48 h). Sore throat with fever: back with a doctor's written clearance. Jaundice or a Big 6 diagnosis: back only when the health department approves</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
